--- a/figures/partitioning_figures/partitioning_per_class_per_mol.xlsx
+++ b/figures/partitioning_figures/partitioning_per_class_per_mol.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="328">
   <si>
     <t>protein_adsorbed</t>
   </si>
@@ -199,7 +199,7 @@
     <t>0.81+/-0</t>
   </si>
   <si>
-    <t>0.850+/-0.010</t>
+    <t>0.860+/-0.010</t>
   </si>
   <si>
     <t>0.95+/-0.06</t>
@@ -214,288 +214,291 @@
     <t>0.890+/-0.020</t>
   </si>
   <si>
+    <t>0.940+/-0.030</t>
+  </si>
+  <si>
+    <t>0.860+/-0.020</t>
+  </si>
+  <si>
+    <t>0.920+/-0.030</t>
+  </si>
+  <si>
+    <t>0.86+/-0.11</t>
+  </si>
+  <si>
+    <t>0.900+/-0.010</t>
+  </si>
+  <si>
+    <t>0.910+/-0.030</t>
+  </si>
+  <si>
+    <t>0.94+/-0.07</t>
+  </si>
+  <si>
+    <t>0.88+/-0.11</t>
+  </si>
+  <si>
+    <t>0.82+/-0.18</t>
+  </si>
+  <si>
+    <t>0.95+/-0</t>
+  </si>
+  <si>
+    <t>0.930+/-0.010</t>
+  </si>
+  <si>
+    <t>0.940+/-0.020</t>
+  </si>
+  <si>
+    <t>0.960+/-0.010</t>
+  </si>
+  <si>
+    <t>0.54+/-0.18</t>
+  </si>
+  <si>
+    <t>0.980+/-0.020</t>
+  </si>
+  <si>
+    <t>0.930+/-0.020</t>
+  </si>
+  <si>
+    <t>0.9+/-0</t>
+  </si>
+  <si>
+    <t>0.87+/-0</t>
+  </si>
+  <si>
+    <t>0.89+/-0</t>
+  </si>
+  <si>
+    <t>0.78+/-0.04</t>
+  </si>
+  <si>
+    <t>0.90+/-0.10</t>
+  </si>
+  <si>
+    <t>0.93+/-0</t>
+  </si>
+  <si>
+    <t>0.970+/-0.020</t>
+  </si>
+  <si>
+    <t>0.90+/-0.06</t>
+  </si>
+  <si>
+    <t>0.95+/-0.04</t>
+  </si>
+  <si>
+    <t>0.940+/-0.010</t>
+  </si>
+  <si>
+    <t>0.950+/-0.020</t>
+  </si>
+  <si>
+    <t>0.86+/-0</t>
+  </si>
+  <si>
+    <t>0.880+/-0.010</t>
+  </si>
+  <si>
+    <t>0.040+/-0.030</t>
+  </si>
+  <si>
+    <t>0.090+/-0.010</t>
+  </si>
+  <si>
+    <t>0.0+/-0</t>
+  </si>
+  <si>
+    <t>0.01+/-0</t>
+  </si>
+  <si>
+    <t>0.03+/-0</t>
+  </si>
+  <si>
+    <t>0.010+/-0.010</t>
+  </si>
+  <si>
+    <t>0.020+/-0.010</t>
+  </si>
+  <si>
+    <t>0.02+/-0</t>
+  </si>
+  <si>
+    <t>0.020+/-0.020</t>
+  </si>
+  <si>
+    <t>0.080+/-0.020</t>
+  </si>
+  <si>
+    <t>0.06+/-0</t>
+  </si>
+  <si>
+    <t>0.23+/-0.12</t>
+  </si>
+  <si>
+    <t>0.090+/-0.020</t>
+  </si>
+  <si>
+    <t>0.08+/-0.08</t>
+  </si>
+  <si>
+    <t>0.12+/-0.04</t>
+  </si>
+  <si>
+    <t>0.09+/-0</t>
+  </si>
+  <si>
+    <t>0.150+/-0.010</t>
+  </si>
+  <si>
+    <t>0.15+/-0</t>
+  </si>
+  <si>
+    <t>0.140+/-0.010</t>
+  </si>
+  <si>
+    <t>0.05+/-0.06</t>
+  </si>
+  <si>
+    <t>0.030+/-0.030</t>
+  </si>
+  <si>
+    <t>0.100+/-0.020</t>
+  </si>
+  <si>
+    <t>0.050+/-0.020</t>
+  </si>
+  <si>
+    <t>0.130+/-0.020</t>
+  </si>
+  <si>
+    <t>0.060+/-0.030</t>
+  </si>
+  <si>
+    <t>0.13+/-0.10</t>
+  </si>
+  <si>
+    <t>0.080+/-0.010</t>
+  </si>
+  <si>
+    <t>0.090+/-0.030</t>
+  </si>
+  <si>
+    <t>0.06+/-0.07</t>
+  </si>
+  <si>
+    <t>0.11+/-0.10</t>
+  </si>
+  <si>
+    <t>0.16+/-0.19</t>
+  </si>
+  <si>
+    <t>0.05+/-0</t>
+  </si>
+  <si>
+    <t>0.050+/-0.010</t>
+  </si>
+  <si>
+    <t>0.030+/-0.020</t>
+  </si>
+  <si>
+    <t>0.46+/-0.18</t>
+  </si>
+  <si>
+    <t>0.060+/-0.020</t>
+  </si>
+  <si>
+    <t>0.100+/-0.010</t>
+  </si>
+  <si>
+    <t>0.12+/-0</t>
+  </si>
+  <si>
+    <t>0.11+/-0</t>
+  </si>
+  <si>
+    <t>0.140+/-0.020</t>
+  </si>
+  <si>
+    <t>0.10+/-0.10</t>
+  </si>
+  <si>
+    <t>0.07+/-0</t>
+  </si>
+  <si>
+    <t>0.10+/-0.06</t>
+  </si>
+  <si>
+    <t>0.05+/-0.04</t>
+  </si>
+  <si>
+    <t>0.060+/-0.010</t>
+  </si>
+  <si>
+    <t>0.08+/-0</t>
+  </si>
+  <si>
+    <t>0.110+/-0.010</t>
+  </si>
+  <si>
+    <t>10FG</t>
+  </si>
+  <si>
+    <t>10MG</t>
+  </si>
+  <si>
+    <t>5FTF</t>
+  </si>
+  <si>
+    <t>5MG</t>
+  </si>
+  <si>
+    <t>ACOA</t>
+  </si>
+  <si>
+    <t>COA</t>
+  </si>
+  <si>
+    <t>DFAD</t>
+  </si>
+  <si>
+    <t>DFMN</t>
+  </si>
+  <si>
+    <t>DRBF</t>
+  </si>
+  <si>
+    <t>FMN</t>
+  </si>
+  <si>
+    <t>NIC</t>
+  </si>
+  <si>
+    <t>NICR</t>
+  </si>
+  <si>
+    <t>PALP</t>
+  </si>
+  <si>
+    <t>RBF</t>
+  </si>
+  <si>
+    <t>THFG</t>
+  </si>
+  <si>
+    <t>TPPH</t>
+  </si>
+  <si>
+    <t>0.98+/-0</t>
+  </si>
+  <si>
+    <t>0.950+/-0.010</t>
+  </si>
+  <si>
     <t>0.930+/-0.030</t>
   </si>
   <si>
-    <t>0.860+/-0.020</t>
-  </si>
-  <si>
-    <t>0.920+/-0.030</t>
-  </si>
-  <si>
-    <t>0.86+/-0.11</t>
-  </si>
-  <si>
-    <t>0.900+/-0.010</t>
-  </si>
-  <si>
-    <t>0.910+/-0.030</t>
-  </si>
-  <si>
-    <t>0.94+/-0.07</t>
-  </si>
-  <si>
-    <t>0.88+/-0.11</t>
-  </si>
-  <si>
-    <t>0.82+/-0.18</t>
-  </si>
-  <si>
-    <t>0.95+/-0</t>
-  </si>
-  <si>
-    <t>0.930+/-0.010</t>
-  </si>
-  <si>
-    <t>0.940+/-0.020</t>
-  </si>
-  <si>
-    <t>0.960+/-0.010</t>
-  </si>
-  <si>
-    <t>0.54+/-0.18</t>
-  </si>
-  <si>
-    <t>0.980+/-0.020</t>
-  </si>
-  <si>
-    <t>0.930+/-0.020</t>
-  </si>
-  <si>
-    <t>0.9+/-0</t>
-  </si>
-  <si>
-    <t>0.87+/-0</t>
-  </si>
-  <si>
-    <t>0.89+/-0</t>
-  </si>
-  <si>
-    <t>0.78+/-0.04</t>
-  </si>
-  <si>
-    <t>0.90+/-0.10</t>
-  </si>
-  <si>
-    <t>0.93+/-0</t>
-  </si>
-  <si>
-    <t>0.970+/-0.020</t>
-  </si>
-  <si>
-    <t>0.90+/-0.06</t>
-  </si>
-  <si>
-    <t>0.95+/-0.04</t>
-  </si>
-  <si>
-    <t>0.940+/-0.010</t>
-  </si>
-  <si>
-    <t>0.950+/-0.020</t>
-  </si>
-  <si>
-    <t>0.86+/-0</t>
-  </si>
-  <si>
-    <t>0.880+/-0.010</t>
-  </si>
-  <si>
-    <t>0.040+/-0.030</t>
-  </si>
-  <si>
-    <t>0.090+/-0.010</t>
-  </si>
-  <si>
-    <t>0.0+/-0</t>
-  </si>
-  <si>
-    <t>0.01+/-0</t>
-  </si>
-  <si>
-    <t>0.03+/-0</t>
-  </si>
-  <si>
-    <t>0.010+/-0.010</t>
-  </si>
-  <si>
-    <t>0.020+/-0.010</t>
-  </si>
-  <si>
-    <t>0.02+/-0</t>
-  </si>
-  <si>
-    <t>0.020+/-0.020</t>
-  </si>
-  <si>
-    <t>0.080+/-0.020</t>
-  </si>
-  <si>
-    <t>0.06+/-0</t>
-  </si>
-  <si>
-    <t>0.23+/-0.12</t>
-  </si>
-  <si>
-    <t>0.090+/-0.020</t>
-  </si>
-  <si>
-    <t>0.08+/-0.09</t>
-  </si>
-  <si>
-    <t>0.12+/-0.04</t>
-  </si>
-  <si>
-    <t>0.09+/-0</t>
-  </si>
-  <si>
-    <t>0.150+/-0.010</t>
-  </si>
-  <si>
-    <t>0.15+/-0</t>
-  </si>
-  <si>
-    <t>0.140+/-0.010</t>
-  </si>
-  <si>
-    <t>0.05+/-0.06</t>
-  </si>
-  <si>
-    <t>0.030+/-0.030</t>
-  </si>
-  <si>
-    <t>0.100+/-0.020</t>
-  </si>
-  <si>
-    <t>0.050+/-0.020</t>
-  </si>
-  <si>
-    <t>0.130+/-0.020</t>
-  </si>
-  <si>
-    <t>0.060+/-0.030</t>
-  </si>
-  <si>
-    <t>0.13+/-0.10</t>
-  </si>
-  <si>
-    <t>0.080+/-0.010</t>
-  </si>
-  <si>
-    <t>0.090+/-0.030</t>
-  </si>
-  <si>
-    <t>0.06+/-0.07</t>
-  </si>
-  <si>
-    <t>0.11+/-0.10</t>
-  </si>
-  <si>
-    <t>0.16+/-0.19</t>
-  </si>
-  <si>
-    <t>0.05+/-0</t>
-  </si>
-  <si>
-    <t>0.050+/-0.010</t>
-  </si>
-  <si>
-    <t>0.030+/-0.020</t>
-  </si>
-  <si>
-    <t>0.46+/-0.18</t>
-  </si>
-  <si>
-    <t>0.060+/-0.020</t>
-  </si>
-  <si>
-    <t>0.100+/-0.010</t>
-  </si>
-  <si>
-    <t>0.12+/-0</t>
-  </si>
-  <si>
-    <t>0.11+/-0</t>
-  </si>
-  <si>
-    <t>0.140+/-0.020</t>
-  </si>
-  <si>
-    <t>0.10+/-0.10</t>
-  </si>
-  <si>
-    <t>0.07+/-0</t>
-  </si>
-  <si>
-    <t>0.10+/-0.06</t>
-  </si>
-  <si>
-    <t>0.05+/-0.04</t>
-  </si>
-  <si>
-    <t>0.060+/-0.010</t>
-  </si>
-  <si>
-    <t>0.08+/-0</t>
-  </si>
-  <si>
-    <t>0.110+/-0.010</t>
-  </si>
-  <si>
-    <t>10FG</t>
-  </si>
-  <si>
-    <t>10MG</t>
-  </si>
-  <si>
-    <t>5FTF</t>
-  </si>
-  <si>
-    <t>5MG</t>
-  </si>
-  <si>
-    <t>ACOA</t>
-  </si>
-  <si>
-    <t>COA</t>
-  </si>
-  <si>
-    <t>DFAD</t>
-  </si>
-  <si>
-    <t>DFMN</t>
-  </si>
-  <si>
-    <t>DRBF</t>
-  </si>
-  <si>
-    <t>FMN</t>
-  </si>
-  <si>
-    <t>NIC</t>
-  </si>
-  <si>
-    <t>NICR</t>
-  </si>
-  <si>
-    <t>PALP</t>
-  </si>
-  <si>
-    <t>RBF</t>
-  </si>
-  <si>
-    <t>THFG</t>
-  </si>
-  <si>
-    <t>TPPH</t>
-  </si>
-  <si>
-    <t>0.98+/-0</t>
-  </si>
-  <si>
-    <t>0.950+/-0.010</t>
-  </si>
-  <si>
     <t>0.890+/-0.010</t>
   </si>
   <si>
@@ -589,7 +592,7 @@
     <t>SPER</t>
   </si>
   <si>
-    <t>0.52+/-0.04</t>
+    <t>0.53+/-0.04</t>
   </si>
   <si>
     <t>0.170+/-0.020</t>
@@ -934,9 +937,6 @@
     <t>0.31+/-0</t>
   </si>
   <si>
-    <t>0.25+/-0</t>
-  </si>
-  <si>
     <t>0.290+/-0.010</t>
   </si>
   <si>
@@ -947,9 +947,6 @@
   </si>
   <si>
     <t>0.460+/-0.010</t>
-  </si>
-  <si>
-    <t>0.660+/-0.030</t>
   </si>
   <si>
     <t>0.700+/-0.020</t>
@@ -2096,7 +2093,7 @@
         <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2107,7 +2104,7 @@
         <v>157</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D4" t="s">
         <v>100</v>
@@ -2121,7 +2118,7 @@
         <v>157</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
         <v>99</v>
@@ -2166,7 +2163,7 @@
         <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2188,10 +2185,10 @@
         <v>148</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>158</v>
       </c>
       <c r="C10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D10" t="s">
         <v>117</v>
@@ -2202,7 +2199,7 @@
         <v>149</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C11" t="s">
         <v>100</v>
@@ -2216,10 +2213,10 @@
         <v>150</v>
       </c>
       <c r="B12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D12" t="s">
         <v>103</v>
@@ -2230,13 +2227,13 @@
         <v>151</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" t="s">
         <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2244,13 +2241,13 @@
         <v>152</v>
       </c>
       <c r="B14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2258,7 +2255,7 @@
         <v>153</v>
       </c>
       <c r="B15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C15" t="s">
         <v>98</v>
@@ -2278,7 +2275,7 @@
         <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2286,13 +2283,13 @@
         <v>155</v>
       </c>
       <c r="B17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2318,16 +2315,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
         <v>124</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2353,27 +2350,27 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D3" t="s">
         <v>97</v>
@@ -2381,13 +2378,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D4" t="s">
         <v>134</v>
@@ -2395,27 +2392,27 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D6" t="s">
         <v>108</v>
@@ -2423,13 +2420,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D7" t="s">
         <v>108</v>
@@ -2437,27 +2434,27 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D9" t="s">
         <v>100</v>
@@ -2465,13 +2462,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
         <v>129</v>
@@ -2479,13 +2476,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D11" t="s">
         <v>124</v>
@@ -2493,30 +2490,30 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C12" t="s">
         <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C13" t="s">
         <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -2542,27 +2539,27 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>129</v>
@@ -2570,13 +2567,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D4" t="s">
         <v>108</v>
@@ -2584,41 +2581,41 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D7" t="s">
         <v>130</v>
@@ -2626,13 +2623,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D8" t="s">
         <v>139</v>
@@ -2640,13 +2637,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D9" t="s">
         <v>108</v>
@@ -2654,27 +2651,27 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D11" t="s">
         <v>129</v>
@@ -2682,41 +2679,41 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C12" t="s">
         <v>134</v>
       </c>
       <c r="D12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D14" t="s">
         <v>108</v>
@@ -2724,13 +2721,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D15" t="s">
         <v>129</v>
@@ -2738,13 +2735,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B16" t="s">
+        <v>252</v>
+      </c>
+      <c r="C16" t="s">
         <v>251</v>
-      </c>
-      <c r="C16" t="s">
-        <v>250</v>
       </c>
       <c r="D16" t="s">
         <v>108</v>
@@ -2752,13 +2749,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D17" t="s">
         <v>129</v>
@@ -2766,41 +2763,41 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B18" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C19" t="s">
         <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D20" t="s">
         <v>139</v>
@@ -2808,13 +2805,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C21" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D21" t="s">
         <v>139</v>
@@ -2822,13 +2819,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D22" t="s">
         <v>111</v>
@@ -2836,27 +2833,27 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D24" t="s">
         <v>132</v>
@@ -2885,13 +2882,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D2" t="s">
         <v>138</v>
@@ -2899,27 +2896,27 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C3" t="s">
         <v>308</v>
       </c>
       <c r="D3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C4" t="s">
         <v>298</v>
-      </c>
-      <c r="C4" t="s">
-        <v>297</v>
       </c>
       <c r="D4" t="s">
         <v>110</v>
@@ -2927,13 +2924,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C5" t="s">
-        <v>309</v>
+        <v>253</v>
       </c>
       <c r="D5" t="s">
         <v>94</v>
@@ -2941,13 +2938,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D6" t="s">
         <v>138</v>
@@ -2955,13 +2952,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D7" t="s">
         <v>138</v>
@@ -2969,13 +2966,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D8" t="s">
         <v>138</v>
@@ -2983,27 +2980,27 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D10" t="s">
         <v>119</v>
@@ -3011,13 +3008,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" t="s">
         <v>176</v>
-      </c>
-      <c r="C11" t="s">
-        <v>175</v>
       </c>
       <c r="D11" t="s">
         <v>103</v>
@@ -3025,27 +3022,27 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D12" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D13" t="s">
         <v>119</v>
@@ -3053,13 +3050,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C14" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D14" t="s">
         <v>138</v>
@@ -3067,13 +3064,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -3081,13 +3078,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B16" t="s">
-        <v>304</v>
+        <v>196</v>
       </c>
       <c r="C16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D16" t="s">
         <v>129</v>
@@ -3095,27 +3092,27 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B17" t="s">
         <v>305</v>
       </c>
       <c r="C17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B18" t="s">
         <v>306</v>
       </c>
       <c r="C18" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D18" t="s">
         <v>119</v>
@@ -3123,13 +3120,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B19" t="s">
         <v>307</v>
       </c>
       <c r="C19" t="s">
-        <v>308</v>
+        <v>206</v>
       </c>
       <c r="D19" t="s">
         <v>139</v>
@@ -3137,13 +3134,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D20" t="s">
         <v>134</v>
@@ -3172,63 +3169,63 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C4" t="s">
         <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C5" t="s">
         <v>326</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>327</v>
-      </c>
-      <c r="D5" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
         <v>96</v>

--- a/figures/partitioning_figures/partitioning_per_class_per_mol.xlsx
+++ b/figures/partitioning_figures/partitioning_per_class_per_mol.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Nucleotides" sheetId="1" r:id="rId1"/>
     <sheet name="Cofactors" sheetId="2" r:id="rId2"/>
-    <sheet name="Lipids" sheetId="3" r:id="rId3"/>
+    <sheet name="Fatty Acids" sheetId="3" r:id="rId3"/>
     <sheet name="Other_Metabolites" sheetId="4" r:id="rId4"/>
     <sheet name="Carbohydrates" sheetId="5" r:id="rId5"/>
     <sheet name="Amino_Acids" sheetId="6" r:id="rId6"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="355">
   <si>
     <t>protein_adsorbed</t>
   </si>
@@ -175,835 +175,916 @@
     <t>UTP</t>
   </si>
   <si>
-    <t>0.73+/-0.11</t>
-  </si>
-  <si>
-    <t>0.820+/-0.030</t>
-  </si>
-  <si>
-    <t>0.92+/-0.09</t>
-  </si>
-  <si>
-    <t>0.910+/-0.010</t>
-  </si>
-  <si>
-    <t>0.88+/-0.04</t>
-  </si>
-  <si>
-    <t>0.91+/-0</t>
-  </si>
-  <si>
-    <t>0.840+/-0.010</t>
-  </si>
-  <si>
-    <t>0.81+/-0</t>
-  </si>
-  <si>
-    <t>0.860+/-0.010</t>
-  </si>
-  <si>
-    <t>0.95+/-0.06</t>
-  </si>
-  <si>
-    <t>0.990+/-0.010</t>
-  </si>
-  <si>
-    <t>0.960+/-0.030</t>
-  </si>
-  <si>
-    <t>0.890+/-0.020</t>
-  </si>
-  <si>
-    <t>0.940+/-0.030</t>
-  </si>
-  <si>
-    <t>0.860+/-0.020</t>
-  </si>
-  <si>
-    <t>0.920+/-0.030</t>
-  </si>
-  <si>
-    <t>0.86+/-0.11</t>
-  </si>
-  <si>
-    <t>0.900+/-0.010</t>
-  </si>
-  <si>
-    <t>0.910+/-0.030</t>
-  </si>
-  <si>
-    <t>0.94+/-0.07</t>
-  </si>
-  <si>
-    <t>0.88+/-0.11</t>
-  </si>
-  <si>
-    <t>0.82+/-0.18</t>
-  </si>
-  <si>
-    <t>0.95+/-0</t>
-  </si>
-  <si>
-    <t>0.930+/-0.010</t>
+    <t>0.330+/-0.020</t>
+  </si>
+  <si>
+    <t>0.67+/-0.05</t>
+  </si>
+  <si>
+    <t>0.27+/-0.12</t>
+  </si>
+  <si>
+    <t>0.430+/-0.020</t>
+  </si>
+  <si>
+    <t>0.470+/-0.010</t>
+  </si>
+  <si>
+    <t>0.410+/-0.010</t>
+  </si>
+  <si>
+    <t>0.440+/-0.010</t>
+  </si>
+  <si>
+    <t>0.460+/-0.010</t>
+  </si>
+  <si>
+    <t>0.370+/-0.020</t>
+  </si>
+  <si>
+    <t>0.62+/-0.16</t>
+  </si>
+  <si>
+    <t>0.6+/-0.4</t>
+  </si>
+  <si>
+    <t>0.65+/-0.07</t>
+  </si>
+  <si>
+    <t>0.53+/-0.10</t>
+  </si>
+  <si>
+    <t>0.53+/-0.13</t>
+  </si>
+  <si>
+    <t>0.49+/-0.09</t>
+  </si>
+  <si>
+    <t>0.56+/-0.08</t>
+  </si>
+  <si>
+    <t>0.440+/-0.030</t>
+  </si>
+  <si>
+    <t>0.58+/-0.04</t>
+  </si>
+  <si>
+    <t>0.46+/-0.08</t>
+  </si>
+  <si>
+    <t>0.72+/-0.13</t>
+  </si>
+  <si>
+    <t>0.38+/-0.11</t>
+  </si>
+  <si>
+    <t>0.73+/-0.22</t>
+  </si>
+  <si>
+    <t>0.35+/-0.05</t>
+  </si>
+  <si>
+    <t>0.58+/-0.10</t>
+  </si>
+  <si>
+    <t>0.68+/-0.06</t>
+  </si>
+  <si>
+    <t>0.63+/-0.05</t>
+  </si>
+  <si>
+    <t>0.07+/-0.07</t>
+  </si>
+  <si>
+    <t>0.70+/-0.20</t>
+  </si>
+  <si>
+    <t>0.570+/-0.030</t>
+  </si>
+  <si>
+    <t>0.4+/-0.4</t>
+  </si>
+  <si>
+    <t>0.42+/-0</t>
+  </si>
+  <si>
+    <t>0.380+/-0.020</t>
+  </si>
+  <si>
+    <t>0.510+/-0.030</t>
+  </si>
+  <si>
+    <t>0.46+/-0.23</t>
+  </si>
+  <si>
+    <t>0.340+/-0.010</t>
+  </si>
+  <si>
+    <t>0.49+/-0.08</t>
+  </si>
+  <si>
+    <t>0.29+/-0.16</t>
+  </si>
+  <si>
+    <t>0.62+/-0.08</t>
+  </si>
+  <si>
+    <t>0.65+/-0.04</t>
+  </si>
+  <si>
+    <t>0.520+/-0.010</t>
+  </si>
+  <si>
+    <t>0.52+/-0</t>
+  </si>
+  <si>
+    <t>0.490+/-0.010</t>
+  </si>
+  <si>
+    <t>0.480+/-0.030</t>
+  </si>
+  <si>
+    <t>0.640+/-0.010</t>
+  </si>
+  <si>
+    <t>0.480+/-0.010</t>
+  </si>
+  <si>
+    <t>0.390+/-0.010</t>
+  </si>
+  <si>
+    <t>0.040+/-0.030</t>
+  </si>
+  <si>
+    <t>0.090+/-0.020</t>
+  </si>
+  <si>
+    <t>0.0+/-0</t>
+  </si>
+  <si>
+    <t>0.01+/-0</t>
+  </si>
+  <si>
+    <t>0.03+/-0</t>
+  </si>
+  <si>
+    <t>0.010+/-0.010</t>
+  </si>
+  <si>
+    <t>0.02+/-0</t>
+  </si>
+  <si>
+    <t>0.020+/-0.020</t>
+  </si>
+  <si>
+    <t>0.020+/-0.010</t>
+  </si>
+  <si>
+    <t>0.06+/-0</t>
+  </si>
+  <si>
+    <t>0.630+/-0.010</t>
+  </si>
+  <si>
+    <t>0.24+/-0.05</t>
+  </si>
+  <si>
+    <t>0.73+/-0.12</t>
+  </si>
+  <si>
+    <t>0.560+/-0.020</t>
+  </si>
+  <si>
+    <t>0.530+/-0.010</t>
+  </si>
+  <si>
+    <t>0.590+/-0.010</t>
+  </si>
+  <si>
+    <t>0.560+/-0.010</t>
+  </si>
+  <si>
+    <t>0.510+/-0.010</t>
+  </si>
+  <si>
+    <t>0.630+/-0.020</t>
+  </si>
+  <si>
+    <t>0.38+/-0.16</t>
+  </si>
+  <si>
+    <t>0.34+/-0.07</t>
+  </si>
+  <si>
+    <t>0.46+/-0.10</t>
+  </si>
+  <si>
+    <t>0.46+/-0.14</t>
+  </si>
+  <si>
+    <t>0.42+/-0.08</t>
+  </si>
+  <si>
+    <t>0.550+/-0.030</t>
+  </si>
+  <si>
+    <t>0.40+/-0.04</t>
+  </si>
+  <si>
+    <t>0.54+/-0.08</t>
+  </si>
+  <si>
+    <t>0.28+/-0.14</t>
+  </si>
+  <si>
+    <t>0.62+/-0.10</t>
+  </si>
+  <si>
+    <t>0.25+/-0.23</t>
+  </si>
+  <si>
+    <t>0.65+/-0.05</t>
+  </si>
+  <si>
+    <t>0.41+/-0.10</t>
+  </si>
+  <si>
+    <t>0.30+/-0.06</t>
+  </si>
+  <si>
+    <t>0.36+/-0.05</t>
+  </si>
+  <si>
+    <t>0.92+/-0.07</t>
+  </si>
+  <si>
+    <t>0.30+/-0.21</t>
+  </si>
+  <si>
+    <t>0.420+/-0.030</t>
+  </si>
+  <si>
+    <t>0.57+/-0</t>
+  </si>
+  <si>
+    <t>0.570+/-0.020</t>
+  </si>
+  <si>
+    <t>0.620+/-0.020</t>
+  </si>
+  <si>
+    <t>0.53+/-0.22</t>
+  </si>
+  <si>
+    <t>0.650+/-0.010</t>
+  </si>
+  <si>
+    <t>0.51+/-0.08</t>
+  </si>
+  <si>
+    <t>0.71+/-0.16</t>
+  </si>
+  <si>
+    <t>0.38+/-0.08</t>
+  </si>
+  <si>
+    <t>0.33+/-0.04</t>
+  </si>
+  <si>
+    <t>0.48+/-0</t>
+  </si>
+  <si>
+    <t>0.300+/-0.010</t>
+  </si>
+  <si>
+    <t>0.600+/-0.010</t>
+  </si>
+  <si>
+    <t>10FG</t>
+  </si>
+  <si>
+    <t>10MG</t>
+  </si>
+  <si>
+    <t>5FTF</t>
+  </si>
+  <si>
+    <t>5MG</t>
+  </si>
+  <si>
+    <t>ACOA</t>
+  </si>
+  <si>
+    <t>COA</t>
+  </si>
+  <si>
+    <t>DFAD</t>
+  </si>
+  <si>
+    <t>DFMN</t>
+  </si>
+  <si>
+    <t>DRBF</t>
+  </si>
+  <si>
+    <t>FMN</t>
+  </si>
+  <si>
+    <t>NIC</t>
+  </si>
+  <si>
+    <t>NICR</t>
+  </si>
+  <si>
+    <t>PALP</t>
+  </si>
+  <si>
+    <t>RBF</t>
+  </si>
+  <si>
+    <t>THFG</t>
+  </si>
+  <si>
+    <t>TPPH</t>
+  </si>
+  <si>
+    <t>0.690+/-0.030</t>
+  </si>
+  <si>
+    <t>0.390+/-0.030</t>
+  </si>
+  <si>
+    <t>0.770+/-0.020</t>
+  </si>
+  <si>
+    <t>0.790+/-0.010</t>
+  </si>
+  <si>
+    <t>0.570+/-0.010</t>
+  </si>
+  <si>
+    <t>0.320+/-0.030</t>
+  </si>
+  <si>
+    <t>0.29+/-0.12</t>
+  </si>
+  <si>
+    <t>0.59+/-0.06</t>
+  </si>
+  <si>
+    <t>0.210+/-0.030</t>
+  </si>
+  <si>
+    <t>0.550+/-0.010</t>
+  </si>
+  <si>
+    <t>0.500+/-0.030</t>
+  </si>
+  <si>
+    <t>0.750+/-0.020</t>
+  </si>
+  <si>
+    <t>0.420+/-0.020</t>
+  </si>
+  <si>
+    <t>0.030+/-0.010</t>
+  </si>
+  <si>
+    <t>0.000+/-0.010</t>
+  </si>
+  <si>
+    <t>0.260+/-0.010</t>
+  </si>
+  <si>
+    <t>0.330+/-0.010</t>
+  </si>
+  <si>
+    <t>0.310+/-0.020</t>
+  </si>
+  <si>
+    <t>0.310+/-0.030</t>
+  </si>
+  <si>
+    <t>0.610+/-0.030</t>
+  </si>
+  <si>
+    <t>0.200+/-0.020</t>
+  </si>
+  <si>
+    <t>0.180+/-0.010</t>
+  </si>
+  <si>
+    <t>0.430+/-0.010</t>
+  </si>
+  <si>
+    <t>0.440+/-0.020</t>
+  </si>
+  <si>
+    <t>0.680+/-0.020</t>
+  </si>
+  <si>
+    <t>0.70+/-0.12</t>
+  </si>
+  <si>
+    <t>0.61+/-0.10</t>
+  </si>
+  <si>
+    <t>0.39+/-0.06</t>
+  </si>
+  <si>
+    <t>0.15+/-0</t>
+  </si>
+  <si>
+    <t>0.780+/-0.030</t>
+  </si>
+  <si>
+    <t>0.110+/-0.010</t>
+  </si>
+  <si>
+    <t>0.220+/-0.020</t>
+  </si>
+  <si>
+    <t>0.270+/-0.010</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>0.540+/-0.010</t>
+  </si>
+  <si>
+    <t>0.04+/-0</t>
+  </si>
+  <si>
+    <t>0.420+/-0.010</t>
+  </si>
+  <si>
+    <t>3GPP</t>
+  </si>
+  <si>
+    <t>ACEH</t>
+  </si>
+  <si>
+    <t>ACEP</t>
+  </si>
+  <si>
+    <t>ACET</t>
+  </si>
+  <si>
+    <t>DHAP</t>
+  </si>
+  <si>
+    <t>G3H</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>O2</t>
+  </si>
+  <si>
+    <t>PEP</t>
+  </si>
+  <si>
+    <t>PYR</t>
+  </si>
+  <si>
+    <t>SAM</t>
+  </si>
+  <si>
+    <t>SPER</t>
+  </si>
+  <si>
+    <t>0.42+/-0.04</t>
+  </si>
+  <si>
+    <t>0.160+/-0.020</t>
+  </si>
+  <si>
+    <t>0.370+/-0.010</t>
+  </si>
+  <si>
+    <t>0.2+/-0</t>
+  </si>
+  <si>
+    <t>0.41+/-0</t>
+  </si>
+  <si>
+    <t>0.39+/-0</t>
+  </si>
+  <si>
+    <t>0.220+/-0.010</t>
+  </si>
+  <si>
+    <t>0.170+/-0.010</t>
+  </si>
+  <si>
+    <t>0.540+/-0.030</t>
+  </si>
+  <si>
+    <t>0.31+/-0</t>
+  </si>
+  <si>
+    <t>0.29+/-0.04</t>
+  </si>
+  <si>
+    <t>0.060+/-0.020</t>
+  </si>
+  <si>
+    <t>0.800+/-0.020</t>
+  </si>
+  <si>
+    <t>0.54+/-0</t>
+  </si>
+  <si>
+    <t>0.75+/-0</t>
+  </si>
+  <si>
+    <t>0.46+/-0</t>
+  </si>
+  <si>
+    <t>0.660+/-0.010</t>
+  </si>
+  <si>
+    <t>0.800+/-0.010</t>
+  </si>
+  <si>
+    <t>0.280+/-0.010</t>
+  </si>
+  <si>
+    <t>0.61+/-0</t>
+  </si>
+  <si>
+    <t>0.25+/-0.06</t>
+  </si>
+  <si>
+    <t>0.1+/-0</t>
+  </si>
+  <si>
+    <t>0.05+/-0</t>
+  </si>
+  <si>
+    <t>0.13+/-0</t>
+  </si>
+  <si>
+    <t>0.12+/-0</t>
+  </si>
+  <si>
+    <t>0.180+/-0.030</t>
+  </si>
+  <si>
+    <t>0.08+/-0</t>
+  </si>
+  <si>
+    <t>0.71+/-0.04</t>
   </si>
   <si>
     <t>0.940+/-0.020</t>
   </si>
   <si>
-    <t>0.960+/-0.010</t>
-  </si>
-  <si>
-    <t>0.54+/-0.18</t>
-  </si>
-  <si>
-    <t>0.980+/-0.020</t>
-  </si>
-  <si>
-    <t>0.930+/-0.020</t>
-  </si>
-  <si>
-    <t>0.9+/-0</t>
-  </si>
-  <si>
-    <t>0.87+/-0</t>
-  </si>
-  <si>
-    <t>0.89+/-0</t>
-  </si>
-  <si>
-    <t>0.78+/-0.04</t>
-  </si>
-  <si>
-    <t>0.90+/-0.10</t>
-  </si>
-  <si>
-    <t>0.93+/-0</t>
-  </si>
-  <si>
-    <t>0.970+/-0.020</t>
-  </si>
-  <si>
-    <t>0.90+/-0.06</t>
-  </si>
-  <si>
-    <t>0.95+/-0.04</t>
-  </si>
-  <si>
-    <t>0.940+/-0.010</t>
-  </si>
-  <si>
-    <t>0.950+/-0.020</t>
-  </si>
-  <si>
-    <t>0.86+/-0</t>
-  </si>
-  <si>
-    <t>0.880+/-0.010</t>
-  </si>
-  <si>
-    <t>0.040+/-0.030</t>
+    <t>3PG</t>
+  </si>
+  <si>
+    <t>DR1P</t>
+  </si>
+  <si>
+    <t>DR5P</t>
+  </si>
+  <si>
+    <t>E4P</t>
+  </si>
+  <si>
+    <t>F6P</t>
+  </si>
+  <si>
+    <t>FBP</t>
+  </si>
+  <si>
+    <t>G1P</t>
+  </si>
+  <si>
+    <t>G3P</t>
+  </si>
+  <si>
+    <t>G6P</t>
+  </si>
+  <si>
+    <t>GL2P</t>
+  </si>
+  <si>
+    <t>GL6P</t>
+  </si>
+  <si>
+    <t>GLR</t>
+  </si>
+  <si>
+    <t>GN6P</t>
+  </si>
+  <si>
+    <t>M6P</t>
+  </si>
+  <si>
+    <t>MANA</t>
+  </si>
+  <si>
+    <t>MN6P</t>
+  </si>
+  <si>
+    <t>PRP</t>
+  </si>
+  <si>
+    <t>PRPP</t>
+  </si>
+  <si>
+    <t>R1P</t>
+  </si>
+  <si>
+    <t>R5P</t>
+  </si>
+  <si>
+    <t>RI5P</t>
+  </si>
+  <si>
+    <t>S7P</t>
+  </si>
+  <si>
+    <t>X5P</t>
+  </si>
+  <si>
+    <t>0.500+/-0.010</t>
+  </si>
+  <si>
+    <t>0.430+/-0.030</t>
+  </si>
+  <si>
+    <t>0.55+/-0</t>
+  </si>
+  <si>
+    <t>0.35+/-0</t>
+  </si>
+  <si>
+    <t>0.530+/-0.020</t>
+  </si>
+  <si>
+    <t>0.320+/-0.010</t>
+  </si>
+  <si>
+    <t>0.21+/-0</t>
+  </si>
+  <si>
+    <t>0.510+/-0.020</t>
+  </si>
+  <si>
+    <t>0.290+/-0.020</t>
+  </si>
+  <si>
+    <t>0.550+/-0.020</t>
+  </si>
+  <si>
+    <t>0.47+/-0.04</t>
+  </si>
+  <si>
+    <t>0.490+/-0.020</t>
+  </si>
+  <si>
+    <t>0.500+/-0.020</t>
+  </si>
+  <si>
+    <t>0.44+/-0.05</t>
+  </si>
+  <si>
+    <t>0.190+/-0.010</t>
+  </si>
+  <si>
+    <t>0.380+/-0.010</t>
+  </si>
+  <si>
+    <t>0.240+/-0.020</t>
+  </si>
+  <si>
+    <t>0.380+/-0.030</t>
+  </si>
+  <si>
+    <t>0.23+/-0</t>
+  </si>
+  <si>
+    <t>0.270+/-0.030</t>
+  </si>
+  <si>
+    <t>0.07+/-0</t>
+  </si>
+  <si>
+    <t>0.66+/-0</t>
+  </si>
+  <si>
+    <t>0.240+/-0.030</t>
+  </si>
+  <si>
+    <t>0.590+/-0.020</t>
+  </si>
+  <si>
+    <t>0.260+/-0.020</t>
+  </si>
+  <si>
+    <t>0.070+/-0.010</t>
+  </si>
+  <si>
+    <t>0.100+/-0.020</t>
+  </si>
+  <si>
+    <t>0.300+/-0.030</t>
+  </si>
+  <si>
+    <t>0.280+/-0.020</t>
+  </si>
+  <si>
+    <t>0.250+/-0.010</t>
+  </si>
+  <si>
+    <t>0.35+/-0.04</t>
+  </si>
+  <si>
+    <t>0.16+/-0</t>
+  </si>
+  <si>
+    <t>0.17+/-0</t>
+  </si>
+  <si>
+    <t>0.25+/-0</t>
+  </si>
+  <si>
+    <t>0.190+/-0.020</t>
+  </si>
+  <si>
+    <t>0.200+/-0.030</t>
+  </si>
+  <si>
+    <t>0.610+/-0.010</t>
+  </si>
+  <si>
+    <t>0.120+/-0.010</t>
+  </si>
+  <si>
+    <t>0.46+/-0.05</t>
+  </si>
+  <si>
+    <t>0.410+/-0.020</t>
+  </si>
+  <si>
+    <t>0.200+/-0.010</t>
+  </si>
+  <si>
+    <t>0.210+/-0.010</t>
+  </si>
+  <si>
+    <t>0.290+/-0.010</t>
+  </si>
+  <si>
+    <t>0.310+/-0.010</t>
+  </si>
+  <si>
+    <t>LALA</t>
+  </si>
+  <si>
+    <t>LARG</t>
+  </si>
+  <si>
+    <t>LASP</t>
+  </si>
+  <si>
+    <t>LCYS</t>
+  </si>
+  <si>
+    <t>LGLN</t>
+  </si>
+  <si>
+    <t>LGLU</t>
+  </si>
+  <si>
+    <t>LGLY</t>
+  </si>
+  <si>
+    <t>LHIS</t>
+  </si>
+  <si>
+    <t>LILE</t>
+  </si>
+  <si>
+    <t>LLEU</t>
+  </si>
+  <si>
+    <t>LLYS</t>
+  </si>
+  <si>
+    <t>LMET</t>
+  </si>
+  <si>
+    <t>LPHE</t>
+  </si>
+  <si>
+    <t>LPRO</t>
+  </si>
+  <si>
+    <t>LSER</t>
+  </si>
+  <si>
+    <t>LTHR</t>
+  </si>
+  <si>
+    <t>LTRP</t>
+  </si>
+  <si>
+    <t>LTYR</t>
+  </si>
+  <si>
+    <t>LVAL</t>
+  </si>
+  <si>
+    <t>0.240+/-0.010</t>
+  </si>
+  <si>
+    <t>0.24+/-0</t>
+  </si>
+  <si>
+    <t>0.19+/-0</t>
+  </si>
+  <si>
+    <t>0.230+/-0.010</t>
+  </si>
+  <si>
+    <t>0.37+/-0.05</t>
+  </si>
+  <si>
+    <t>0.300+/-0.020</t>
+  </si>
+  <si>
+    <t>0.650+/-0.030</t>
+  </si>
+  <si>
+    <t>0.700+/-0.020</t>
+  </si>
+  <si>
+    <t>0.62+/-0</t>
+  </si>
+  <si>
+    <t>0.7+/-0</t>
+  </si>
+  <si>
+    <t>0.730+/-0.010</t>
+  </si>
+  <si>
+    <t>0.43+/-0</t>
+  </si>
+  <si>
+    <t>0.48+/-0.05</t>
+  </si>
+  <si>
+    <t>0.130+/-0.010</t>
+  </si>
+  <si>
+    <t>0.11+/-0</t>
+  </si>
+  <si>
+    <t>0.30+/-0.04</t>
+  </si>
+  <si>
+    <t>0.120+/-0.020</t>
   </si>
   <si>
     <t>0.090+/-0.010</t>
   </si>
   <si>
-    <t>0.0+/-0</t>
-  </si>
-  <si>
-    <t>0.01+/-0</t>
-  </si>
-  <si>
-    <t>0.03+/-0</t>
-  </si>
-  <si>
-    <t>0.010+/-0.010</t>
-  </si>
-  <si>
-    <t>0.020+/-0.010</t>
-  </si>
-  <si>
-    <t>0.02+/-0</t>
-  </si>
-  <si>
-    <t>0.020+/-0.020</t>
-  </si>
-  <si>
-    <t>0.080+/-0.020</t>
-  </si>
-  <si>
-    <t>0.06+/-0</t>
-  </si>
-  <si>
-    <t>0.23+/-0.12</t>
-  </si>
-  <si>
-    <t>0.090+/-0.020</t>
-  </si>
-  <si>
-    <t>0.08+/-0.08</t>
-  </si>
-  <si>
-    <t>0.12+/-0.04</t>
-  </si>
-  <si>
-    <t>0.09+/-0</t>
-  </si>
-  <si>
     <t>0.150+/-0.010</t>
   </si>
   <si>
-    <t>0.15+/-0</t>
-  </si>
-  <si>
     <t>0.140+/-0.010</t>
   </si>
   <si>
-    <t>0.05+/-0.06</t>
-  </si>
-  <si>
-    <t>0.030+/-0.030</t>
-  </si>
-  <si>
-    <t>0.100+/-0.020</t>
-  </si>
-  <si>
-    <t>0.050+/-0.020</t>
-  </si>
-  <si>
-    <t>0.130+/-0.020</t>
-  </si>
-  <si>
-    <t>0.060+/-0.030</t>
-  </si>
-  <si>
-    <t>0.13+/-0.10</t>
-  </si>
-  <si>
-    <t>0.080+/-0.010</t>
-  </si>
-  <si>
-    <t>0.090+/-0.030</t>
-  </si>
-  <si>
-    <t>0.06+/-0.07</t>
-  </si>
-  <si>
-    <t>0.11+/-0.10</t>
-  </si>
-  <si>
-    <t>0.16+/-0.19</t>
-  </si>
-  <si>
-    <t>0.05+/-0</t>
-  </si>
-  <si>
-    <t>0.050+/-0.010</t>
-  </si>
-  <si>
-    <t>0.030+/-0.020</t>
-  </si>
-  <si>
-    <t>0.46+/-0.18</t>
-  </si>
-  <si>
-    <t>0.060+/-0.020</t>
-  </si>
-  <si>
-    <t>0.100+/-0.010</t>
-  </si>
-  <si>
-    <t>0.12+/-0</t>
-  </si>
-  <si>
-    <t>0.11+/-0</t>
-  </si>
-  <si>
-    <t>0.140+/-0.020</t>
-  </si>
-  <si>
-    <t>0.10+/-0.10</t>
-  </si>
-  <si>
-    <t>0.07+/-0</t>
-  </si>
-  <si>
-    <t>0.10+/-0.06</t>
-  </si>
-  <si>
-    <t>0.05+/-0.04</t>
-  </si>
-  <si>
-    <t>0.060+/-0.010</t>
-  </si>
-  <si>
-    <t>0.08+/-0</t>
-  </si>
-  <si>
-    <t>0.110+/-0.010</t>
-  </si>
-  <si>
-    <t>10FG</t>
-  </si>
-  <si>
-    <t>10MG</t>
-  </si>
-  <si>
-    <t>5FTF</t>
-  </si>
-  <si>
-    <t>5MG</t>
-  </si>
-  <si>
-    <t>ACOA</t>
-  </si>
-  <si>
-    <t>COA</t>
-  </si>
-  <si>
-    <t>DFAD</t>
-  </si>
-  <si>
-    <t>DFMN</t>
-  </si>
-  <si>
-    <t>DRBF</t>
-  </si>
-  <si>
-    <t>FMN</t>
-  </si>
-  <si>
-    <t>NIC</t>
-  </si>
-  <si>
-    <t>NICR</t>
-  </si>
-  <si>
-    <t>PALP</t>
-  </si>
-  <si>
-    <t>RBF</t>
-  </si>
-  <si>
-    <t>THFG</t>
-  </si>
-  <si>
-    <t>TPPH</t>
+    <t>0.160+/-0.010</t>
+  </si>
+  <si>
+    <t>DPP</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>NH4</t>
+  </si>
+  <si>
+    <t>PO4</t>
+  </si>
+  <si>
+    <t>0.33+/-0</t>
+  </si>
+  <si>
+    <t>0.37+/-0</t>
   </si>
   <si>
     <t>0.98+/-0</t>
-  </si>
-  <si>
-    <t>0.950+/-0.010</t>
-  </si>
-  <si>
-    <t>0.930+/-0.030</t>
-  </si>
-  <si>
-    <t>0.890+/-0.010</t>
-  </si>
-  <si>
-    <t>0.680+/-0.020</t>
-  </si>
-  <si>
-    <t>0.710+/-0.010</t>
-  </si>
-  <si>
-    <t>0.600+/-0.010</t>
-  </si>
-  <si>
-    <t>0.900+/-0.020</t>
-  </si>
-  <si>
-    <t>0.560+/-0.020</t>
-  </si>
-  <si>
-    <t>0.030+/-0.010</t>
-  </si>
-  <si>
-    <t>0.000+/-0.010</t>
-  </si>
-  <si>
-    <t>0.260+/-0.010</t>
-  </si>
-  <si>
-    <t>0.340+/-0.010</t>
-  </si>
-  <si>
-    <t>0.310+/-0.020</t>
-  </si>
-  <si>
-    <t>0.040+/-0.010</t>
-  </si>
-  <si>
-    <t>0.080+/-0.030</t>
-  </si>
-  <si>
-    <t>0.280+/-0.010</t>
-  </si>
-  <si>
-    <t>0.070+/-0.010</t>
-  </si>
-  <si>
-    <t>0.13+/-0</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>0.730+/-0.010</t>
-  </si>
-  <si>
-    <t>0.210+/-0.010</t>
-  </si>
-  <si>
-    <t>3GPP</t>
-  </si>
-  <si>
-    <t>ACEH</t>
-  </si>
-  <si>
-    <t>ACEP</t>
-  </si>
-  <si>
-    <t>ACET</t>
-  </si>
-  <si>
-    <t>DHAP</t>
-  </si>
-  <si>
-    <t>G3H</t>
-  </si>
-  <si>
-    <t>LAC</t>
-  </si>
-  <si>
-    <t>O2</t>
-  </si>
-  <si>
-    <t>PEP</t>
-  </si>
-  <si>
-    <t>PYR</t>
-  </si>
-  <si>
-    <t>SAM</t>
-  </si>
-  <si>
-    <t>SPER</t>
-  </si>
-  <si>
-    <t>0.53+/-0.04</t>
-  </si>
-  <si>
-    <t>0.170+/-0.020</t>
-  </si>
-  <si>
-    <t>0.39+/-0</t>
-  </si>
-  <si>
-    <t>0.21+/-0</t>
-  </si>
-  <si>
-    <t>0.45+/-0</t>
-  </si>
-  <si>
-    <t>0.430+/-0.010</t>
-  </si>
-  <si>
-    <t>0.250+/-0.010</t>
-  </si>
-  <si>
-    <t>0.180+/-0.010</t>
-  </si>
-  <si>
-    <t>0.620+/-0.020</t>
-  </si>
-  <si>
-    <t>0.34+/-0</t>
-  </si>
-  <si>
-    <t>0.900+/-0.030</t>
-  </si>
-  <si>
-    <t>0.49+/-0.04</t>
-  </si>
-  <si>
-    <t>0.340+/-0.030</t>
-  </si>
-  <si>
-    <t>0.800+/-0.020</t>
-  </si>
-  <si>
-    <t>0.54+/-0</t>
-  </si>
-  <si>
-    <t>0.75+/-0</t>
-  </si>
-  <si>
-    <t>0.46+/-0</t>
-  </si>
-  <si>
-    <t>0.480+/-0.010</t>
-  </si>
-  <si>
-    <t>0.660+/-0.010</t>
-  </si>
-  <si>
-    <t>0.800+/-0.010</t>
-  </si>
-  <si>
-    <t>0.61+/-0</t>
-  </si>
-  <si>
-    <t>0.140+/-0.030</t>
-  </si>
-  <si>
-    <t>0.04+/-0</t>
-  </si>
-  <si>
-    <t>0.1+/-0</t>
-  </si>
-  <si>
-    <t>0.100+/-0.030</t>
-  </si>
-  <si>
-    <t>0.50+/-0.04</t>
-  </si>
-  <si>
-    <t>3PG</t>
-  </si>
-  <si>
-    <t>DR1P</t>
-  </si>
-  <si>
-    <t>DR5P</t>
-  </si>
-  <si>
-    <t>E4P</t>
-  </si>
-  <si>
-    <t>F6P</t>
-  </si>
-  <si>
-    <t>FBP</t>
-  </si>
-  <si>
-    <t>G1P</t>
-  </si>
-  <si>
-    <t>G3P</t>
-  </si>
-  <si>
-    <t>G6P</t>
-  </si>
-  <si>
-    <t>GL2P</t>
-  </si>
-  <si>
-    <t>GL6P</t>
-  </si>
-  <si>
-    <t>GLR</t>
-  </si>
-  <si>
-    <t>GN6P</t>
-  </si>
-  <si>
-    <t>M6P</t>
-  </si>
-  <si>
-    <t>MANA</t>
-  </si>
-  <si>
-    <t>MN6P</t>
-  </si>
-  <si>
-    <t>PRP</t>
-  </si>
-  <si>
-    <t>PRPP</t>
-  </si>
-  <si>
-    <t>R1P</t>
-  </si>
-  <si>
-    <t>R5P</t>
-  </si>
-  <si>
-    <t>RI5P</t>
-  </si>
-  <si>
-    <t>S7P</t>
-  </si>
-  <si>
-    <t>X5P</t>
-  </si>
-  <si>
-    <t>0.530+/-0.010</t>
-  </si>
-  <si>
-    <t>0.670+/-0.020</t>
-  </si>
-  <si>
-    <t>0.51+/-0.04</t>
-  </si>
-  <si>
-    <t>0.580+/-0.010</t>
-  </si>
-  <si>
-    <t>0.68+/-0</t>
-  </si>
-  <si>
-    <t>0.560+/-0.010</t>
-  </si>
-  <si>
-    <t>0.4+/-0</t>
-  </si>
-  <si>
-    <t>0.66+/-0</t>
-  </si>
-  <si>
-    <t>0.62+/-0.04</t>
-  </si>
-  <si>
-    <t>0.650+/-0.010</t>
-  </si>
-  <si>
-    <t>0.24+/-0</t>
-  </si>
-  <si>
-    <t>0.670+/-0.030</t>
-  </si>
-  <si>
-    <t>0.590+/-0.020</t>
-  </si>
-  <si>
-    <t>0.320+/-0.020</t>
-  </si>
-  <si>
-    <t>0.650+/-0.030</t>
-  </si>
-  <si>
-    <t>0.74+/-0.04</t>
-  </si>
-  <si>
-    <t>0.77+/-0.04</t>
-  </si>
-  <si>
-    <t>0.580+/-0.020</t>
-  </si>
-  <si>
-    <t>0.590+/-0.010</t>
-  </si>
-  <si>
-    <t>0.52+/-0.06</t>
-  </si>
-  <si>
-    <t>0.190+/-0.010</t>
-  </si>
-  <si>
-    <t>0.38+/-0</t>
-  </si>
-  <si>
-    <t>0.240+/-0.020</t>
-  </si>
-  <si>
-    <t>0.380+/-0.030</t>
-  </si>
-  <si>
-    <t>0.320+/-0.010</t>
-  </si>
-  <si>
-    <t>0.2+/-0</t>
-  </si>
-  <si>
-    <t>0.330+/-0.010</t>
-  </si>
-  <si>
-    <t>0.52+/-0</t>
-  </si>
-  <si>
-    <t>0.23+/-0</t>
-  </si>
-  <si>
-    <t>0.270+/-0.030</t>
-  </si>
-  <si>
-    <t>0.250+/-0.030</t>
-  </si>
-  <si>
-    <t>0.260+/-0.020</t>
-  </si>
-  <si>
-    <t>0.300+/-0.030</t>
-  </si>
-  <si>
-    <t>0.220+/-0.010</t>
-  </si>
-  <si>
-    <t>0.280+/-0.020</t>
-  </si>
-  <si>
-    <t>0.14+/-0</t>
-  </si>
-  <si>
-    <t>0.120+/-0.020</t>
-  </si>
-  <si>
-    <t>0.19+/-0.05</t>
-  </si>
-  <si>
-    <t>0.16+/-0</t>
-  </si>
-  <si>
-    <t>LALA</t>
-  </si>
-  <si>
-    <t>LARG</t>
-  </si>
-  <si>
-    <t>LASP</t>
-  </si>
-  <si>
-    <t>LCYS</t>
-  </si>
-  <si>
-    <t>LGLN</t>
-  </si>
-  <si>
-    <t>LGLU</t>
-  </si>
-  <si>
-    <t>LGLY</t>
-  </si>
-  <si>
-    <t>LHIS</t>
-  </si>
-  <si>
-    <t>LILE</t>
-  </si>
-  <si>
-    <t>LLEU</t>
-  </si>
-  <si>
-    <t>LLYS</t>
-  </si>
-  <si>
-    <t>LMET</t>
-  </si>
-  <si>
-    <t>LPHE</t>
-  </si>
-  <si>
-    <t>LPRO</t>
-  </si>
-  <si>
-    <t>LSER</t>
-  </si>
-  <si>
-    <t>LTHR</t>
-  </si>
-  <si>
-    <t>LTRP</t>
-  </si>
-  <si>
-    <t>LTYR</t>
-  </si>
-  <si>
-    <t>LVAL</t>
-  </si>
-  <si>
-    <t>0.26+/-0</t>
-  </si>
-  <si>
-    <t>0.35+/-0</t>
-  </si>
-  <si>
-    <t>0.510+/-0.010</t>
-  </si>
-  <si>
-    <t>0.210+/-0.020</t>
-  </si>
-  <si>
-    <t>0.3+/-0</t>
-  </si>
-  <si>
-    <t>0.22+/-0</t>
-  </si>
-  <si>
-    <t>0.500+/-0.010</t>
-  </si>
-  <si>
-    <t>0.31+/-0</t>
-  </si>
-  <si>
-    <t>0.290+/-0.010</t>
-  </si>
-  <si>
-    <t>0.44+/-0.06</t>
-  </si>
-  <si>
-    <t>0.430+/-0.020</t>
-  </si>
-  <si>
-    <t>0.460+/-0.010</t>
-  </si>
-  <si>
-    <t>0.700+/-0.020</t>
-  </si>
-  <si>
-    <t>0.620+/-0.010</t>
-  </si>
-  <si>
-    <t>0.7+/-0</t>
-  </si>
-  <si>
-    <t>0.420+/-0.020</t>
-  </si>
-  <si>
-    <t>0.670+/-0.010</t>
-  </si>
-  <si>
-    <t>0.43+/-0</t>
-  </si>
-  <si>
-    <t>0.640+/-0.010</t>
-  </si>
-  <si>
-    <t>0.410+/-0.010</t>
-  </si>
-  <si>
-    <t>0.48+/-0.05</t>
-  </si>
-  <si>
-    <t>0.19+/-0</t>
-  </si>
-  <si>
-    <t>0.150+/-0.030</t>
-  </si>
-  <si>
-    <t>DPP</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>NH4</t>
-  </si>
-  <si>
-    <t>PO4</t>
-  </si>
-  <si>
-    <t>0.400+/-0.010</t>
-  </si>
-  <si>
-    <t>0.360+/-0.010</t>
-  </si>
-  <si>
-    <t>0.230+/-0.020</t>
   </si>
 </sst>
 </file>
@@ -1383,10 +1464,10 @@
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1397,10 +1478,10 @@
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1411,10 +1492,10 @@
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1425,10 +1506,10 @@
         <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1439,10 +1520,10 @@
         <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1453,10 +1534,10 @@
         <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1467,10 +1548,10 @@
         <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1481,10 +1562,10 @@
         <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1495,10 +1576,10 @@
         <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1509,10 +1590,10 @@
         <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1523,10 +1604,10 @@
         <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1537,10 +1618,10 @@
         <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1551,10 +1632,10 @@
         <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1565,10 +1646,10 @@
         <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1579,10 +1660,10 @@
         <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1593,10 +1674,10 @@
         <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1607,10 +1688,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1621,10 +1702,10 @@
         <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1635,10 +1716,10 @@
         <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1649,10 +1730,10 @@
         <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1663,10 +1744,10 @@
         <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1677,10 +1758,10 @@
         <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1691,10 +1772,10 @@
         <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1705,10 +1786,10 @@
         <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1719,10 +1800,10 @@
         <v>75</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1733,10 +1814,10 @@
         <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1747,10 +1828,10 @@
         <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1761,10 +1842,10 @@
         <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1775,10 +1856,10 @@
         <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1786,13 +1867,13 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1800,13 +1881,13 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1814,13 +1895,13 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D33" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1831,10 +1912,10 @@
         <v>82</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1845,10 +1926,10 @@
         <v>83</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1859,10 +1940,10 @@
         <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D36" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1873,10 +1954,10 @@
         <v>85</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D37" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1887,10 +1968,10 @@
         <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1901,10 +1982,10 @@
         <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D39" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1915,10 +1996,10 @@
         <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1926,13 +2007,13 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D41" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1940,13 +2021,13 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D42" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1954,13 +2035,13 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D43" t="s">
         <v>95</v>
-      </c>
-      <c r="D43" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1968,13 +2049,13 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C44" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1982,13 +2063,13 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1996,13 +2077,13 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D46" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2010,13 +2091,13 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2024,13 +2105,13 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D48" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2038,13 +2119,13 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C49" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D49" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2070,226 +2151,226 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B10" t="s">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B11" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="C12" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D14" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>173</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B17" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D17" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2315,16 +2396,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>197</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2350,170 +2431,170 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="C2" t="s">
-        <v>202</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="B3" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="C3" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="C4" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="D5" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C6" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="C7" t="s">
-        <v>207</v>
+        <v>143</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="C8" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D8" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="B9" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="C9" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C11" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="B12" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -2539,324 +2620,324 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>263</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="D2" t="s">
-        <v>274</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="B3" t="s">
-        <v>239</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="B5" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="C5" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="D5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="B6" t="s">
-        <v>242</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D6" t="s">
-        <v>213</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C7" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B8" t="s">
-        <v>244</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>265</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="B9" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="C9" t="s">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="B10" t="s">
-        <v>246</v>
+        <v>134</v>
       </c>
       <c r="C10" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="D10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B11" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="C11" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="B12" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>283</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="B13" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="C13" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="D13" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="B14" t="s">
-        <v>250</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="B15" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="C15" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="B16" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="B17" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="C17" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="B18" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
+        <v>288</v>
       </c>
       <c r="D18" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="B19" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>289</v>
       </c>
       <c r="D19" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="B20" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="C20" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="B21" t="s">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>304</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s">
-        <v>256</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s">
-        <v>257</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>196</v>
+        <v>292</v>
       </c>
       <c r="D23" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="C24" t="s">
-        <v>202</v>
+        <v>293</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2882,268 +2963,268 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="B2" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="B3" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="C3" t="s">
-        <v>308</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="B4" t="s">
-        <v>299</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="B5" t="s">
-        <v>270</v>
+        <v>217</v>
       </c>
       <c r="C5" t="s">
-        <v>253</v>
+        <v>332</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="B6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D6" t="s">
         <v>300</v>
-      </c>
-      <c r="C6" t="s">
-        <v>309</v>
-      </c>
-      <c r="D6" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="B7" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="C7" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="B8" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="C8" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="B9" t="s">
-        <v>195</v>
+        <v>271</v>
       </c>
       <c r="C9" t="s">
-        <v>312</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>304</v>
       </c>
       <c r="C10" t="s">
-        <v>313</v>
+        <v>227</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>287</v>
+        <v>316</v>
       </c>
       <c r="B11" t="s">
-        <v>177</v>
+        <v>328</v>
       </c>
       <c r="C11" t="s">
-        <v>176</v>
+        <v>336</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="B12" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="C12" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="D12" t="s">
-        <v>302</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="B13" t="s">
-        <v>172</v>
+        <v>329</v>
       </c>
       <c r="C13" t="s">
-        <v>315</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>290</v>
+        <v>319</v>
       </c>
       <c r="B14" t="s">
-        <v>303</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>316</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="B15" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C15" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="B16" t="s">
-        <v>196</v>
+        <v>303</v>
       </c>
       <c r="C16" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="B17" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="C17" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="D17" t="s">
-        <v>213</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="B18" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="C18" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="B19" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="C19" t="s">
-        <v>206</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="B20" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="C20" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -3169,72 +3250,72 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="B2" t="s">
-        <v>260</v>
+        <v>352</v>
       </c>
       <c r="C2" t="s">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="B3" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="C3" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="D3" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="B4" t="s">
-        <v>257</v>
+        <v>174</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>325</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="B5" t="s">
-        <v>325</v>
+        <v>268</v>
       </c>
       <c r="C5" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="D5" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>156</v>
+        <v>354</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
